--- a/rules/CORE-000504/negative/01/data/unit-test-coreid-CG0283-negative.xlsx
+++ b/rules/CORE-000504/negative/01/data/unit-test-coreid-CG0283-negative.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\Verisian\core-contributor\rules\CORE-000504\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890E2E9F-7325-4143-AA1B-330886BE0950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A02DBB-CD4B-4C1C-9506-AAE110E9A3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="37">
   <si>
     <t>Product</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>2023-00-00</t>
+  </si>
+  <si>
+    <t>TEST</t>
   </si>
 </sst>
 </file>
@@ -634,7 +637,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -822,20 +825,84 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="A10" s="1">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1">
+        <v>11</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -847,7 +914,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -1027,6 +1094,40 @@
         <v>35</v>
       </c>
     </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="10">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/rules/CORE-000504/negative/01/data/unit-test-coreid-CG0283-negative.xlsx
+++ b/rules/CORE-000504/negative/01/data/unit-test-coreid-CG0283-negative.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -62,26 +62,13 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -100,12 +87,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -113,18 +94,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -148,7 +117,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -157,9 +126,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -736,7 +702,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="str">
@@ -759,55 +725,55 @@
       <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="6" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="6" t="str">
+      <c r="C2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="5" t="str">
         <v>Trial Summary Parameter Short Name</v>
       </c>
-      <c r="E2" s="6" t="str">
+      <c r="E2" s="5" t="str">
         <v>Parameter Value</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="str">
+      <c r="A3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="B3" s="6" t="str">
+      <c r="B3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="C3" s="6" t="str">
+      <c r="C3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="D3" s="6" t="str">
+      <c r="D3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="E3" s="6" t="str">
+      <c r="E3" s="5" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>2</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>8</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="6" t="str">
         <v>CDISCCORE01</v>
       </c>
       <c r="B5" s="4" t="str">
@@ -816,15 +782,15 @@
       <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="D5" s="8" t="str">
+      <c r="D5" s="7" t="str">
         <v>DCUTDTC</v>
       </c>
-      <c r="E5" s="9" t="str">
+      <c r="E5" s="7" t="str">
         <v>2023-02-30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="str">
+      <c r="A6" s="6" t="str">
         <v>CDISCCORE01</v>
       </c>
       <c r="B6" s="4" t="str">
@@ -841,7 +807,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="str">
+      <c r="A7" s="6" t="str">
         <v>CDISCCORE01</v>
       </c>
       <c r="B7" s="4" t="str">
@@ -858,7 +824,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="str">
+      <c r="A8" s="6" t="str">
         <v>CDISCCORE01</v>
       </c>
       <c r="B8" s="4" t="str">
@@ -867,15 +833,15 @@
       <c r="C8" s="4">
         <v>1</v>
       </c>
-      <c r="D8" s="9" t="str">
+      <c r="D8" s="7" t="str">
         <v>DCUTDTC</v>
       </c>
-      <c r="E8" s="9" t="str">
+      <c r="E8" s="7" t="str">
         <v>2023-01-32</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="str">
+      <c r="A9" s="6" t="str">
         <v>CDISCCORE01</v>
       </c>
       <c r="B9" s="4" t="str">
@@ -884,15 +850,15 @@
       <c r="C9" s="4">
         <v>1</v>
       </c>
-      <c r="D9" s="9" t="str">
+      <c r="D9" s="7" t="str">
         <v>DCUTDTC</v>
       </c>
-      <c r="E9" s="9" t="str">
+      <c r="E9" s="7" t="str">
         <v>2023-04-31</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="str">
+      <c r="A10" s="6" t="str">
         <v>CDISCCORE01</v>
       </c>
       <c r="B10" s="4" t="str">
@@ -901,50 +867,16 @@
       <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="D10" s="9" t="str">
+      <c r="D10" s="7" t="str">
         <v>DCUTDTC</v>
       </c>
-      <c r="E10" s="9" t="str">
+      <c r="E10" s="7" t="str">
         <v>2023-00-00</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="str">
-        <v>CDISCCORE01</v>
-      </c>
-      <c r="B11" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="str">
-        <v>DCUTDTC</v>
-      </c>
-      <c r="E11" s="4">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="str">
-        <v>CDISCCORE01</v>
-      </c>
-      <c r="B12" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C12" s="4">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4" t="str">
-        <v>DCUTDTC</v>
-      </c>
-      <c r="E12" s="4" t="str">
-        <v>TEST</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/CORE-000504/negative/01/data/unit-test-coreid-CG0283-negative.xlsx
+++ b/rules/CORE-000504/negative/01/data/unit-test-coreid-CG0283-negative.xlsx
@@ -1,43 +1,152 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\Verisian\core-contributor\rules\CORE-000504\negative\01\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870DEA4F-8906-441B-ACE1-327663FA9A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="Validation" sheetId="3" r:id="rId3"/>
     <sheet name="ts.xpt" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="37">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>ts.xpt</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameters</t>
+  </si>
+  <si>
+    <t>Error group</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>Error level</t>
+  </si>
+  <si>
+    <t>Row num</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Error value</t>
+  </si>
+  <si>
+    <t>Record</t>
+  </si>
+  <si>
+    <t>TSPARMCD</t>
+  </si>
+  <si>
+    <t>DCUTDTC</t>
+  </si>
+  <si>
+    <t>TSVAL</t>
+  </si>
+  <si>
+    <t>2023-02-30</t>
+  </si>
+  <si>
+    <t>2023-01-32</t>
+  </si>
+  <si>
+    <t>2023-04-31</t>
+  </si>
+  <si>
+    <t>2023-00-00</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>TSSEQ</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Short Name</t>
+  </si>
+  <si>
+    <t>Parameter Value</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCCORE01</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>AGEMAX</t>
+  </si>
+  <si>
+    <t>2023-02-28T09:11</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -46,18 +155,9 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
     </font>
     <font>
       <sz val="11"/>
@@ -70,42 +170,28 @@
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <bgColor/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -114,24 +200,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs>
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -456,427 +550,492 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Product</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Version</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>sdtmig</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>3-3</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Filename</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Label</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="B2" s="4" t="str">
-        <v>Trial Summary Parameters</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError sqref="A1:B2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>Error group</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>Sheet</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>Error level</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>Row num</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>Variable</v>
-      </c>
-      <c r="F1" s="3" t="str">
-        <v>Error value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="C2" s="4" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2">
         <v>5</v>
       </c>
-      <c r="E2" s="4" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F2" s="4" t="str">
-        <v>DCUTDTC</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4">
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="C3" s="4" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2">
         <v>5</v>
       </c>
-      <c r="E3" s="4" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="F3" s="4" t="str">
-        <v>2023-02-30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4">
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="C4" s="4" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F4" s="4" t="str">
-        <v>DCUTDTC</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4">
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="C5" s="4" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2">
         <v>8</v>
       </c>
-      <c r="E5" s="4" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="F5" s="4" t="str">
-        <v>2023-01-32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4">
+      <c r="E5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="C6" s="4" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2">
         <v>9</v>
       </c>
-      <c r="E6" s="4" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F6" s="4" t="str">
-        <v>DCUTDTC</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4">
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="C7" s="4" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2">
         <v>9</v>
       </c>
-      <c r="E7" s="4" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="F7" s="4" t="str">
-        <v>2023-04-31</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4">
+      <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="C8" s="4" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2">
         <v>10</v>
       </c>
-      <c r="E8" s="4" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="F8" s="4" t="str">
-        <v>DCUTDTC</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4">
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>4</v>
       </c>
-      <c r="B9" s="4" t="str">
-        <v>ts.xpt</v>
-      </c>
-      <c r="C9" s="4" t="str">
-        <v>Record</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2">
         <v>10</v>
       </c>
-      <c r="E9" s="4" t="str">
-        <v>TSVAL</v>
-      </c>
-      <c r="F9" s="4" t="str">
-        <v>2023-00-00</v>
+      <c r="E9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError sqref="A1:F9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="str">
-        <v>STUDYID</v>
-      </c>
-      <c r="B1" s="3" t="str">
-        <v>DOMAIN</v>
-      </c>
-      <c r="C1" s="3" t="str">
-        <v>TSSEQ</v>
-      </c>
-      <c r="D1" s="3" t="str">
-        <v>TSPARMCD</v>
-      </c>
-      <c r="E1" s="3" t="str">
-        <v>TSVAL</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="str">
-        <v>Study Identifier</v>
-      </c>
-      <c r="B2" s="5" t="str">
-        <v>Domain Abbreviation</v>
-      </c>
-      <c r="C2" s="5" t="str">
-        <v>Sequence Number</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <v>Trial Summary Parameter Short Name</v>
-      </c>
-      <c r="E2" s="5" t="str">
-        <v>Parameter Value</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <v>Num</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
-        <v>Char</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>2</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>8</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="str">
-        <v>CDISCCORE01</v>
-      </c>
-      <c r="B5" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C5" s="4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="7" t="str">
-        <v>DCUTDTC</v>
-      </c>
-      <c r="E5" s="7" t="str">
-        <v>2023-02-30</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="str">
-        <v>CDISCCORE01</v>
-      </c>
-      <c r="B6" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="D5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2">
         <v>2</v>
       </c>
-      <c r="D6" s="4" t="str">
-        <v>AGEMAX</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2">
         <v>99</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="str">
-        <v>CDISCCORE01</v>
-      </c>
-      <c r="B7" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C7" s="4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="str">
-        <v>DCUTDTC</v>
-      </c>
-      <c r="E7" s="4" t="str">
-        <v>2023-02-28T09:11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="str">
-        <v>CDISCCORE01</v>
-      </c>
-      <c r="B8" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="2">
         <v>1</v>
       </c>
-      <c r="D8" s="7" t="str">
-        <v>DCUTDTC</v>
-      </c>
-      <c r="E8" s="7" t="str">
-        <v>2023-01-32</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="str">
-        <v>CDISCCORE01</v>
-      </c>
-      <c r="B9" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="D8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2">
         <v>1</v>
       </c>
-      <c r="D9" s="7" t="str">
-        <v>DCUTDTC</v>
-      </c>
-      <c r="E9" s="7" t="str">
-        <v>2023-04-31</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="str">
-        <v>CDISCCORE01</v>
-      </c>
-      <c r="B10" s="4" t="str">
-        <v>TS</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="D9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2">
         <v>1</v>
       </c>
-      <c r="D10" s="7" t="str">
-        <v>DCUTDTC</v>
-      </c>
-      <c r="E10" s="7" t="str">
-        <v>2023-00-00</v>
+      <c r="D10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E10"/>
+    <ignoredError sqref="A1:E10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>